--- a/www/flightdata/xlsx/eoss-311.xlsx
+++ b/www/flightdata/xlsx/eoss-311.xlsx
@@ -3303,7 +3303,7 @@
         <v>28709.72</v>
       </c>
       <c r="I2">
-        <v>559</v>
+        <v>414</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
